--- a/docs/data/jp/xlsx/6857.xlsx
+++ b/docs/data/jp/xlsx/6857.xlsx
@@ -5464,7 +5464,7 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>Profit Loss Before Tax</t>
+          <t>법인세차감전 이익</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
@@ -5621,7 +5621,7 @@
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
         <is>
-          <t>Gain On Sales Of Available For Sale Financial Assets</t>
+          <t>매도가능금융자산 매각이익</t>
         </is>
       </c>
       <c r="P82" s="22" t="n">
@@ -5634,7 +5634,7 @@
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Trade And Other Receivables Ope CF</t>
+          <t>영업채권 및 기타채권 증감액</t>
         </is>
       </c>
       <c r="F83" s="22" t="n">
@@ -5677,7 +5677,7 @@
     <row r="84">
       <c r="A84" s="20" t="inlineStr">
         <is>
-          <t>Decrease Increase In Inventories Ope CF</t>
+          <t>재고자산 증감액</t>
         </is>
       </c>
       <c r="F84" s="22" t="n">
@@ -5720,7 +5720,7 @@
     <row r="85">
       <c r="A85" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Trade And Other Payables Ope CF</t>
+          <t>영업채무 및 기타채무 증감액</t>
         </is>
       </c>
       <c r="F85" s="22" t="n">
@@ -5763,7 +5763,7 @@
     <row r="86">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>Warranty Provisions</t>
+          <t>제품보증 충당금 증감액</t>
         </is>
       </c>
       <c r="F86" s="22" t="n">
@@ -5806,7 +5806,7 @@
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Advance Receipts Ope CF</t>
+          <t>선수금 증감액</t>
         </is>
       </c>
       <c r="F87" s="22" t="n">
@@ -5840,7 +5840,7 @@
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Retirement Benefit Liability Ope CF</t>
+          <t>퇴직급여부채 증감액</t>
         </is>
       </c>
       <c r="F88" s="22" t="n">
@@ -6055,7 +6055,7 @@
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>Income Taxes Refund Paid Ope CF</t>
+          <t>법인소득세 지급액</t>
         </is>
       </c>
       <c r="F93" s="22" t="n">
@@ -6098,7 +6098,7 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>Net Cash Provided By Used In Operating Activities</t>
+          <t>영업활동 현금흐름 계</t>
         </is>
       </c>
       <c r="F94" s="12" t="n">
@@ -6141,7 +6141,7 @@
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Available For Sale Financial Assets Inv CF</t>
+          <t>매도가능금융자산 매각</t>
         </is>
       </c>
       <c r="P95" s="22" t="n">
@@ -6154,7 +6154,7 @@
     <row r="96">
       <c r="A96" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Available For Sale Financial Assets Inv CF</t>
+          <t>매도가능금융자산 취득</t>
         </is>
       </c>
       <c r="P96" s="22" t="n">
@@ -6167,7 +6167,7 @@
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Equity Instruments Inv CF</t>
+          <t>자본성 금융상품 매각</t>
         </is>
       </c>
       <c r="F97" s="22" t="n">
@@ -6201,7 +6201,7 @@
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Equity Instruments Inv CF</t>
+          <t>자본성 금융상품 취득</t>
         </is>
       </c>
       <c r="F98" s="22" t="n">
@@ -6244,7 +6244,7 @@
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Debt Instruments</t>
+          <t>부채성 금융상품 취득</t>
         </is>
       </c>
       <c r="Q99" s="22" t="n">
@@ -6257,7 +6257,7 @@
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>Purchese Of Debt Instruments Inv CF</t>
+          <t>부채성 금융상품 취득</t>
         </is>
       </c>
       <c r="R100" s="22" t="n">
@@ -6270,7 +6270,7 @@
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Debt Instruments Inv CF</t>
+          <t>부채성 금융상품 매각</t>
         </is>
       </c>
       <c r="S101" s="22" t="n">
@@ -6372,7 +6372,7 @@
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>Purchase Of Intangible Assets Inv CF</t>
+          <t>무형자산 취득 지출</t>
         </is>
       </c>
       <c r="F104" s="22" t="n">
@@ -6459,7 +6459,7 @@
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>Payments For Acquisition Of Subsidiaries Inv CF</t>
+          <t>자회사 취득 지출</t>
         </is>
       </c>
       <c r="F107" s="22" t="n">
@@ -6542,7 +6542,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>Net Cash Provided By Used In Investing Activities</t>
+          <t>투자활동 현금흐름 계</t>
         </is>
       </c>
       <c r="F109" s="12" t="n">
@@ -6635,7 +6635,7 @@
     <row r="112">
       <c r="A112" s="20" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Short Term Borrowings Fin CF</t>
+          <t>단기차입금 순증감액</t>
         </is>
       </c>
       <c r="F112" s="22" t="n">
@@ -6894,7 +6894,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>Net Cash Provided By Used In Financing Activities</t>
+          <t>재무활동 현금흐름 계</t>
         </is>
       </c>
       <c r="F119" s="12" t="n">
@@ -6980,7 +6980,7 @@
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Cash And Cash Equivalents</t>
+          <t>현금및현금성자산 순증감액</t>
         </is>
       </c>
       <c r="F121" s="22" t="n">
@@ -9759,7 +9759,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>Current Assets Other Than Assets Held For Sale CA</t>
+          <t>(소계)</t>
         </is>
       </c>
       <c r="H75" s="12" t="n">
@@ -9869,7 +9869,7 @@
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
         <is>
-          <t>Goodwill And Intangible Assets</t>
+          <t>영업권 및 무형자산</t>
         </is>
       </c>
       <c r="C80" s="22" t="n">
@@ -10149,7 +10149,7 @@
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>Lease Liabilities CL</t>
+          <t>리스부채</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
@@ -10289,7 +10289,7 @@
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>Lease Liabilities NCL</t>
+          <t>리스부채</t>
         </is>
       </c>
       <c r="C95" s="22" t="n">

--- a/docs/data/jp/xlsx/6857.xlsx
+++ b/docs/data/jp/xlsx/6857.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="재무상태표" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터 데이터" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'연간'!$3:$3</definedName>
@@ -21,14 +22,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0%;-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="0.0&quot;x&quot;;-0.0&quot;x&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;년&quot;;-0.0&quot;년&quot;;&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0&quot;일&quot;;-0&quot;일&quot;;&quot;-&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0;\(#,##0.0\);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,11 +122,31 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -149,6 +171,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
       </patternFill>
     </fill>
     <fill>
@@ -195,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -333,7 +360,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1421,7 +1463,7 @@
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>Services Support And Others</t>
+          <t>서비스 외</t>
         </is>
       </c>
       <c r="B10" s="10" t="n"/>
@@ -1949,7 +1991,7 @@
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>Services And Others</t>
+          <t>서비스 외</t>
         </is>
       </c>
       <c r="B16" s="10" t="n"/>
@@ -2207,7 +2249,7 @@
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>Semiconductor And Component Test System Business</t>
+          <t>반도체·부품 테스트 시스템 사업</t>
         </is>
       </c>
       <c r="B19" s="10" t="n"/>
@@ -2467,7 +2509,7 @@
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>Mechatronics System Business</t>
+          <t>메카트로닉스 관련 사업</t>
         </is>
       </c>
       <c r="B22" s="10" t="n"/>
@@ -6238,7 +6280,7 @@
         </is>
       </c>
       <c r="B68" s="27" t="n">
-        <v>34980</v>
+        <v>34930</v>
       </c>
       <c r="C68" s="28" t="n"/>
       <c r="D68" s="29" t="n"/>
@@ -9145,7 +9187,7 @@
     <row r="123">
       <c r="A123" s="18" t="inlineStr">
         <is>
-          <t>Basic Earnings Loss Per Share</t>
+          <t>기본</t>
         </is>
       </c>
       <c r="C123" s="20" t="n">
@@ -9203,7 +9245,7 @@
     <row r="124">
       <c r="A124" s="18" t="inlineStr">
         <is>
-          <t>Diluted Earnings Loss Per Share</t>
+          <t>희석 후</t>
         </is>
       </c>
       <c r="C124" s="20" t="n">
@@ -9557,7 +9599,7 @@
     <row r="130">
       <c r="A130" s="18" t="inlineStr">
         <is>
-          <t>Net Change In Fair Value Of Equity Instruments Designated As Measured At Fair Value Through Other Comprehensive Income Net Of Tax Items That Will Not Be Reclassified To Profit Or Loss OCI</t>
+          <t>기타포괄손익-공정가치 측정 금융자산 공정가치 순변동</t>
         </is>
       </c>
       <c r="C130" s="20" t="n">
@@ -10058,7 +10100,7 @@
     <row r="139">
       <c r="A139" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>서비스 외 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C139" s="20" t="n">
@@ -10184,7 +10226,7 @@
     <row r="142">
       <c r="A142" s="18" t="inlineStr">
         <is>
-          <t>부문 · Intersegment Sales</t>
+          <t>반도체·부품 테스트 시스템 사업 · 부문 간 매출</t>
         </is>
       </c>
       <c r="C142" s="20" t="n">
@@ -10203,7 +10245,7 @@
     <row r="143">
       <c r="A143" s="18" t="inlineStr">
         <is>
-          <t>부문 · Intersegment Sales</t>
+          <t>메카트로닉스 관련 사업 · 부문 간 매출</t>
         </is>
       </c>
       <c r="C143" s="20" t="n">
@@ -10222,7 +10264,7 @@
     <row r="144">
       <c r="A144" s="18" t="inlineStr">
         <is>
-          <t>테스트시스템 사업 · Intersegment Sales</t>
+          <t>테스트시스템 사업 · 부문 간 매출</t>
         </is>
       </c>
       <c r="E144" s="20" t="n">
@@ -10238,7 +10280,7 @@
     <row r="145">
       <c r="A145" s="18" t="inlineStr">
         <is>
-          <t>부문 · Intersegment Sales</t>
+          <t>서비스 외 · 부문 간 매출</t>
         </is>
       </c>
       <c r="E145" s="20" t="n">
@@ -10254,7 +10296,7 @@
     <row r="146">
       <c r="A146" s="18" t="inlineStr">
         <is>
-          <t>테스트시스템 사업 · Intersegment Sales</t>
+          <t>테스트시스템 사업 · 부문 간 매출</t>
         </is>
       </c>
       <c r="G146" s="20" t="n">
@@ -10279,7 +10321,7 @@
     <row r="147">
       <c r="A147" s="18" t="inlineStr">
         <is>
-          <t>부문 · Intersegment Sales</t>
+          <t>서비스 외 · 부문 간 매출</t>
         </is>
       </c>
       <c r="C147" s="20" t="n">
@@ -10313,7 +10355,7 @@
     <row r="148">
       <c r="A148" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Intersegment Sales</t>
+          <t>조정액 · 부문 간 매출</t>
         </is>
       </c>
       <c r="C148" s="20" t="n">
@@ -10359,7 +10401,7 @@
     <row r="149">
       <c r="A149" s="18" t="inlineStr">
         <is>
-          <t>Intersegment Sales</t>
+          <t>부문 간 매출</t>
         </is>
       </c>
       <c r="C149" s="20" t="n">
@@ -10405,7 +10447,7 @@
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>부문 · 합계</t>
+          <t>반도체·부품 테스트 시스템 사업 · 합계</t>
         </is>
       </c>
       <c r="C150" s="20" t="n">
@@ -10440,7 +10482,7 @@
     <row r="152">
       <c r="A152" s="18" t="inlineStr">
         <is>
-          <t>부문 · 합계</t>
+          <t>메카트로닉스 관련 사업 · 합계</t>
         </is>
       </c>
       <c r="C152" s="20" t="n">
@@ -10511,7 +10553,7 @@
     <row r="156">
       <c r="A156" s="18" t="inlineStr">
         <is>
-          <t>부문 · 합계</t>
+          <t>서비스 외 · 합계</t>
         </is>
       </c>
       <c r="E156" s="20" t="n">
@@ -10608,7 +10650,7 @@
     <row r="160">
       <c r="A160" s="18" t="inlineStr">
         <is>
-          <t>부문 · 합계</t>
+          <t>서비스 외 · 합계</t>
         </is>
       </c>
       <c r="C160" s="20" t="n">
@@ -10822,7 +10864,7 @@
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>부문 · Segment Profit Loss</t>
+          <t>반도체·부품 테스트 시스템 사업 · 부문 이익(△손실)(조정 전 영업이익(△손실))</t>
         </is>
       </c>
       <c r="C165" s="20" t="n">
@@ -10885,7 +10927,7 @@
     <row r="168">
       <c r="A168" s="18" t="inlineStr">
         <is>
-          <t>부문 · Segment Profit Loss</t>
+          <t>메카트로닉스 관련 사업 · 부문 이익(△손실)(조정 전 영업이익(△손실))</t>
         </is>
       </c>
       <c r="C168" s="20" t="n">
@@ -10948,7 +10990,7 @@
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>테스트시스템 사업 · Segment Profit Loss</t>
+          <t>테스트시스템 사업 · 부문 이익(△손실)(조정 전 영업이익(△손실))</t>
         </is>
       </c>
       <c r="E171" s="20" t="n">
@@ -11008,7 +11050,7 @@
     <row r="174">
       <c r="A174" s="18" t="inlineStr">
         <is>
-          <t>부문 · Segment Profit Loss</t>
+          <t>서비스 외 · 부문 이익(△손실)(조정 전 영업이익(△손실))</t>
         </is>
       </c>
       <c r="E174" s="20" t="n">
@@ -11068,7 +11110,7 @@
     <row r="177">
       <c r="A177" s="18" t="inlineStr">
         <is>
-          <t>테스트시스템 사업 · Segment Profit Loss</t>
+          <t>테스트시스템 사업 · 부문 이익(△손실)(조정 전 영업이익(△손실))</t>
         </is>
       </c>
       <c r="G177" s="20" t="n">
@@ -11165,7 +11207,7 @@
     <row r="180">
       <c r="A180" s="18" t="inlineStr">
         <is>
-          <t>부문 · Segment Profit Loss</t>
+          <t>서비스 외 · 부문 이익(△손실)(조정 전 영업이익(△손실))</t>
         </is>
       </c>
       <c r="C180" s="20" t="n">
@@ -11283,7 +11325,7 @@
     <row r="183">
       <c r="A183" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Segment Profit Loss</t>
+          <t>조정액 · 부문 이익(△손실)(조정 전 영업이익(△손실))</t>
         </is>
       </c>
       <c r="C183" s="20" t="n">
@@ -11329,7 +11371,7 @@
     <row r="184">
       <c r="A184" s="18" t="inlineStr">
         <is>
-          <t>Segment Profit Loss</t>
+          <t>부문 이익(△손실)(조정 전 영업이익(△손실))</t>
         </is>
       </c>
       <c r="C184" s="20" t="n">
@@ -11375,7 +11417,7 @@
     <row r="185">
       <c r="A185" s="18" t="inlineStr">
         <is>
-          <t>부문 · Adjustment Share Based Compensation Expense</t>
+          <t>반도체·부품 테스트 시스템 사업 · (조정) 주식보상비용</t>
         </is>
       </c>
       <c r="C185" s="20" t="n">
@@ -11394,7 +11436,7 @@
     <row r="186">
       <c r="A186" s="18" t="inlineStr">
         <is>
-          <t>부문 · Adjustment Share Based Compensation Expense</t>
+          <t>메카트로닉스 관련 사업 · (조정) 주식보상비용</t>
         </is>
       </c>
       <c r="C186" s="20" t="n">
@@ -11413,7 +11455,7 @@
     <row r="187">
       <c r="A187" s="18" t="inlineStr">
         <is>
-          <t>테스트시스템 사업 · Adjustment Share Based Compensation Expense</t>
+          <t>테스트시스템 사업 · (조정) 주식보상비용</t>
         </is>
       </c>
       <c r="E187" s="20" t="n">
@@ -11429,7 +11471,7 @@
     <row r="188">
       <c r="A188" s="18" t="inlineStr">
         <is>
-          <t>부문 · Adjustment Share Based Compensation Expense</t>
+          <t>서비스 외 · (조정) 주식보상비용</t>
         </is>
       </c>
       <c r="E188" s="20" t="n">
@@ -11445,7 +11487,7 @@
     <row r="189">
       <c r="A189" s="18" t="inlineStr">
         <is>
-          <t>테스트시스템 사업 · Adjustment Share Based Compensation Expense</t>
+          <t>테스트시스템 사업 · (조정) 주식보상비용</t>
         </is>
       </c>
       <c r="G189" s="20" t="n">
@@ -11470,7 +11512,7 @@
     <row r="190">
       <c r="A190" s="18" t="inlineStr">
         <is>
-          <t>부문 · Adjustment Share Based Compensation Expense</t>
+          <t>서비스 외 · (조정) 주식보상비용</t>
         </is>
       </c>
       <c r="C190" s="20" t="n">
@@ -11504,7 +11546,7 @@
     <row r="191">
       <c r="A191" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Adjustment Share Based Compensation Expense</t>
+          <t>조정액 · (조정) 주식보상비용</t>
         </is>
       </c>
       <c r="C191" s="20" t="n">
@@ -11550,7 +11592,7 @@
     <row r="192">
       <c r="A192" s="18" t="inlineStr">
         <is>
-          <t>Adjustment Share Based Compensation Expense</t>
+          <t>(조정) 주식보상비용</t>
         </is>
       </c>
       <c r="C192" s="20" t="n">
@@ -11596,7 +11638,7 @@
     <row r="193">
       <c r="A193" s="18" t="inlineStr">
         <is>
-          <t>부문 · 영업이익</t>
+          <t>반도체·부품 테스트 시스템 사업 · 영업이익</t>
         </is>
       </c>
       <c r="C193" s="20" t="n">
@@ -11659,7 +11701,7 @@
     <row r="196">
       <c r="A196" s="18" t="inlineStr">
         <is>
-          <t>부문 · 영업이익</t>
+          <t>메카트로닉스 관련 사업 · 영업이익</t>
         </is>
       </c>
       <c r="C196" s="20" t="n">
@@ -11782,7 +11824,7 @@
     <row r="202">
       <c r="A202" s="18" t="inlineStr">
         <is>
-          <t>부문 · 영업이익</t>
+          <t>서비스 외 · 영업이익</t>
         </is>
       </c>
       <c r="E202" s="20" t="n">
@@ -11939,7 +11981,7 @@
     <row r="208">
       <c r="A208" s="18" t="inlineStr">
         <is>
-          <t>부문 · 영업이익</t>
+          <t>서비스 외 · 영업이익</t>
         </is>
       </c>
       <c r="C208" s="20" t="n">
@@ -12265,7 +12307,7 @@
     <row r="215">
       <c r="A215" s="18" t="inlineStr">
         <is>
-          <t>부문 · 금융수익</t>
+          <t>반도체·부품 테스트 시스템 사업 · 금융수익</t>
         </is>
       </c>
       <c r="C215" s="20" t="n">
@@ -12284,7 +12326,7 @@
     <row r="216">
       <c r="A216" s="18" t="inlineStr">
         <is>
-          <t>부문 · 금융수익</t>
+          <t>메카트로닉스 관련 사업 · 금융수익</t>
         </is>
       </c>
       <c r="C216" s="20" t="n">
@@ -12319,7 +12361,7 @@
     <row r="218">
       <c r="A218" s="18" t="inlineStr">
         <is>
-          <t>부문 · 금융수익</t>
+          <t>서비스 외 · 금융수익</t>
         </is>
       </c>
       <c r="E218" s="20" t="n">
@@ -12360,7 +12402,7 @@
     <row r="220">
       <c r="A220" s="18" t="inlineStr">
         <is>
-          <t>부문 · 금융수익</t>
+          <t>서비스 외 · 금융수익</t>
         </is>
       </c>
       <c r="C220" s="20" t="n">
@@ -12538,7 +12580,7 @@
     <row r="224">
       <c r="A224" s="18" t="inlineStr">
         <is>
-          <t>부문 · 금융비용</t>
+          <t>반도체·부품 테스트 시스템 사업 · 금융비용</t>
         </is>
       </c>
       <c r="C224" s="20" t="n">
@@ -12557,7 +12599,7 @@
     <row r="225">
       <c r="A225" s="18" t="inlineStr">
         <is>
-          <t>부문 · 금융비용</t>
+          <t>메카트로닉스 관련 사업 · 금융비용</t>
         </is>
       </c>
       <c r="C225" s="20" t="n">
@@ -12592,7 +12634,7 @@
     <row r="227">
       <c r="A227" s="18" t="inlineStr">
         <is>
-          <t>부문 · 금융비용</t>
+          <t>서비스 외 · 금융비용</t>
         </is>
       </c>
       <c r="E227" s="20" t="n">
@@ -12633,7 +12675,7 @@
     <row r="229">
       <c r="A229" s="18" t="inlineStr">
         <is>
-          <t>부문 · 금융비용</t>
+          <t>서비스 외 · 금융비용</t>
         </is>
       </c>
       <c r="C229" s="20" t="n">
@@ -12811,7 +12853,7 @@
     <row r="233">
       <c r="A233" s="18" t="inlineStr">
         <is>
-          <t>부문 · 법인세비용차감전 중간이익</t>
+          <t>반도체·부품 테스트 시스템 사업 · 법인세비용차감전 중간이익</t>
         </is>
       </c>
       <c r="C233" s="20" t="n">
@@ -12874,7 +12916,7 @@
     <row r="236">
       <c r="A236" s="18" t="inlineStr">
         <is>
-          <t>부문 · 법인세비용차감전 중간이익</t>
+          <t>메카트로닉스 관련 사업 · 법인세비용차감전 중간이익</t>
         </is>
       </c>
       <c r="C236" s="20" t="n">
@@ -12997,7 +13039,7 @@
     <row r="242">
       <c r="A242" s="18" t="inlineStr">
         <is>
-          <t>부문 · 법인세비용차감전 중간이익</t>
+          <t>서비스 외 · 법인세비용차감전 중간이익</t>
         </is>
       </c>
       <c r="E242" s="20" t="n">
@@ -13154,7 +13196,7 @@
     <row r="248">
       <c r="A248" s="18" t="inlineStr">
         <is>
-          <t>부문 · 법인세비용차감전 중간이익</t>
+          <t>서비스 외 · 법인세비용차감전 중간이익</t>
         </is>
       </c>
       <c r="C248" s="20" t="n">
@@ -13380,7 +13422,7 @@
     <row r="254">
       <c r="A254" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>서비스 외 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="E254" s="20" t="n">
@@ -13396,7 +13438,7 @@
     <row r="255">
       <c r="A255" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>반도체·부품 테스트 시스템 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C255" s="20" t="n">
@@ -13415,7 +13457,7 @@
     <row r="256">
       <c r="A256" s="18" t="inlineStr">
         <is>
-          <t>부문 · 외부 고객 매출</t>
+          <t>메카트로닉스 관련 사업 · 외부 고객 매출</t>
         </is>
       </c>
       <c r="C256" s="20" t="n">
@@ -13844,7 +13886,7 @@
     <row r="265">
       <c r="A265" s="18" t="inlineStr">
         <is>
-          <t>Loss Gain On Valuation Of Financial Instruments Ope CF</t>
+          <t>금융상품 평가손익(△는 이익)</t>
         </is>
       </c>
       <c r="I265" s="20" t="n">
@@ -14184,7 +14226,7 @@
     <row r="272">
       <c r="A272" s="18" t="inlineStr">
         <is>
-          <t>Deposits Received Ope CF</t>
+          <t>예수금 증감(△는 감소)</t>
         </is>
       </c>
       <c r="C272" s="20" t="n">
@@ -20281,6 +20323,1578 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C154"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="50" t="inlineStr">
+        <is>
+          <t>어드반테스트 섹터·사업 데이터</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="51" t="inlineStr">
+        <is>
+          <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · pl oku</t>
+        </is>
+      </c>
+      <c r="B4" s="52" t="n"/>
+      <c r="C4" s="52" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B5" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C5" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="54" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B6" s="55" t="n">
+        <v>4777.3</v>
+      </c>
+      <c r="C6" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="54" t="inlineStr">
+        <is>
+          <t>gp</t>
+        </is>
+      </c>
+      <c r="B7" s="55" t="n">
+        <v>3398.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="54" t="inlineStr">
+        <is>
+          <t>sga</t>
+        </is>
+      </c>
+      <c r="B8" s="55" t="n">
+        <v>732.4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="54" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B9" s="55" t="n">
+        <v>2668.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="54" t="inlineStr">
+        <is>
+          <t>pbt</t>
+        </is>
+      </c>
+      <c r="B10" s="55" t="n">
+        <v>2761.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="54" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B11" s="55" t="n">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t>매출총이익률</t>
+        </is>
+      </c>
+      <c r="B12" s="55" t="n">
+        <v>71.09999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="54" t="inlineStr">
+        <is>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="n">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="54" t="inlineStr">
+        <is>
+          <t>EPS yen</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="n">
+        <v>267.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · 상반기 cum oku</t>
+        </is>
+      </c>
+      <c r="B16" s="52" t="n"/>
+      <c r="C16" s="52" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B17" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C17" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="54" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B18" s="55" t="n">
+        <v>8452</v>
+      </c>
+      <c r="C18" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="54" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B19" s="55" t="n">
+        <v>4568.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="54" t="inlineStr">
+        <is>
+          <t>pbt</t>
+        </is>
+      </c>
+      <c r="B20" s="55" t="n">
+        <v>5102.3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="54" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B21" s="55" t="n">
+        <v>3680.8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>other income</t>
+        </is>
+      </c>
+      <c r="B22" s="55" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="54" t="inlineStr">
+        <is>
+          <t>other expense</t>
+        </is>
+      </c>
+      <c r="B23" s="55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="54" t="inlineStr">
+        <is>
+          <t>fin income</t>
+        </is>
+      </c>
+      <c r="B24" s="55" t="n">
+        <v>570.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="54" t="inlineStr">
+        <is>
+          <t>fin cost</t>
+        </is>
+      </c>
+      <c r="B25" s="55" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="54" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="B26" s="55" t="n">
+        <v>1421.5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>sga</t>
+        </is>
+      </c>
+      <c r="B27" s="55" t="n">
+        <v>1394.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="54" t="inlineStr">
+        <is>
+          <t>cogs</t>
+        </is>
+      </c>
+      <c r="B28" s="55" t="n">
+        <v>2498.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="54" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B29" s="55" t="n">
+        <v>508.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · 2Q standalone calc</t>
+        </is>
+      </c>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B32" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C32" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="54" t="inlineStr">
+        <is>
+          <t>fin income</t>
+        </is>
+      </c>
+      <c r="B33" s="55" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="C33" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="54" t="inlineStr">
+        <is>
+          <t>fin cost</t>
+        </is>
+      </c>
+      <c r="B34" s="55" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="54" t="inlineStr">
+        <is>
+          <t>other income</t>
+        </is>
+      </c>
+      <c r="B35" s="55" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="54" t="inlineStr">
+        <is>
+          <t>other expense</t>
+        </is>
+      </c>
+      <c r="B36" s="55" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="54" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="B37" s="55" t="n">
+        <v>828.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · 부문별 2Q oku</t>
+        </is>
+      </c>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B40" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C40" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="54" t="inlineStr">
+        <is>
+          <t>SoC 테스터</t>
+        </is>
+      </c>
+      <c r="B41" s="57" t="n">
+        <v>3533</v>
+      </c>
+      <c r="C41" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="54" t="inlineStr">
+        <is>
+          <t>메모리 테스터</t>
+        </is>
+      </c>
+      <c r="B42" s="57" t="n">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="54" t="inlineStr">
+        <is>
+          <t>기타 시스템</t>
+        </is>
+      </c>
+      <c r="B43" s="57" t="n">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="54" t="inlineStr">
+        <is>
+          <t>테스트 시스템 합계</t>
+        </is>
+      </c>
+      <c r="B44" s="57" t="n">
+        <v>4367</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="54" t="inlineStr">
+        <is>
+          <t>서비스 등</t>
+        </is>
+      </c>
+      <c r="B45" s="57" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · 환율</t>
+        </is>
+      </c>
+      <c r="B47" s="52" t="n"/>
+      <c r="C47" s="52" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B48" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C48" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="54" t="inlineStr">
+        <is>
+          <t>2Q 달러</t>
+        </is>
+      </c>
+      <c r="B49" s="57" t="n">
+        <v>161</v>
+      </c>
+      <c r="C49" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="54" t="inlineStr">
+        <is>
+          <t>2Q 유로</t>
+        </is>
+      </c>
+      <c r="B50" s="57" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="54" t="inlineStr">
+        <is>
+          <t>상반기 달러</t>
+        </is>
+      </c>
+      <c r="B51" s="57" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="54" t="inlineStr">
+        <is>
+          <t>하반기 assume 달러</t>
+        </is>
+      </c>
+      <c r="B52" s="57" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="54" t="inlineStr">
+        <is>
+          <t>하반기 assume 유로</t>
+        </is>
+      </c>
+      <c r="B53" s="57" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="52" t="inlineStr">
+        <is>
+          <t>this_quarter · rd_capex_da_q2_10억엔</t>
+        </is>
+      </c>
+      <c r="B55" s="52" t="n"/>
+      <c r="C55" s="52" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B56" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C56" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="54" t="inlineStr">
+        <is>
+          <t>연구개발비</t>
+        </is>
+      </c>
+      <c r="B57" s="55" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="C57" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="54" t="inlineStr">
+        <is>
+          <t>연구개발비 %</t>
+        </is>
+      </c>
+      <c r="B58" s="55" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="54" t="inlineStr">
+        <is>
+          <t>설비투자</t>
+        </is>
+      </c>
+      <c r="B59" s="55" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="54" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="B60" s="55" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · cf 상반기 oku</t>
+        </is>
+      </c>
+      <c r="B62" s="52" t="n"/>
+      <c r="C62" s="52" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B63" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C63" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="54" t="inlineStr">
+        <is>
+          <t>ocf</t>
+        </is>
+      </c>
+      <c r="B64" s="57" t="n">
+        <v>3070</v>
+      </c>
+      <c r="C64" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="54" t="inlineStr">
+        <is>
+          <t>icf</t>
+        </is>
+      </c>
+      <c r="B65" s="57" t="n">
+        <v>-2109</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="54" t="inlineStr">
+        <is>
+          <t>debt instruments bought</t>
+        </is>
+      </c>
+      <c r="B66" s="57" t="n">
+        <v>-1844</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="54" t="inlineStr">
+        <is>
+          <t>buyback</t>
+        </is>
+      </c>
+      <c r="B67" s="57" t="n">
+        <v>-1059</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="54" t="inlineStr">
+        <is>
+          <t>dividends</t>
+        </is>
+      </c>
+      <c r="B68" s="57" t="n">
+        <v>-218</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="54" t="inlineStr">
+        <is>
+          <t>cb issued</t>
+        </is>
+      </c>
+      <c r="B69" s="57" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="54" t="inlineStr">
+        <is>
+          <t>inventory increase</t>
+        </is>
+      </c>
+      <c r="B70" s="57" t="n">
+        <v>-1195</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="54" t="inlineStr">
+        <is>
+          <t>advances received increase</t>
+        </is>
+      </c>
+      <c r="B71" s="57" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · bs 0930 oku</t>
+        </is>
+      </c>
+      <c r="B73" s="52" t="n"/>
+      <c r="C73" s="52" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B74" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C74" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="54" t="inlineStr">
+        <is>
+          <t>합계 assets</t>
+        </is>
+      </c>
+      <c r="B75" s="57" t="n">
+        <v>17321</v>
+      </c>
+      <c r="C75" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="54" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="B76" s="57" t="n">
+        <v>4018</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="54" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="B77" s="57" t="n">
+        <v>3524</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="54" t="inlineStr">
+        <is>
+          <t>investment securities</t>
+        </is>
+      </c>
+      <c r="B78" s="57" t="n">
+        <v>4326</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="54" t="inlineStr">
+        <is>
+          <t>bonds cb</t>
+        </is>
+      </c>
+      <c r="B79" s="57" t="n">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="54" t="inlineStr">
+        <is>
+          <t>equity</t>
+        </is>
+      </c>
+      <c r="B80" s="57" t="n">
+        <v>11451</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="54" t="inlineStr">
+        <is>
+          <t>equity ratio</t>
+        </is>
+      </c>
+      <c r="B81" s="55" t="n">
+        <v>66.09999999999999</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · company 2Q 예상 july</t>
+        </is>
+      </c>
+      <c r="B83" s="52" t="n"/>
+      <c r="C83" s="52" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B84" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C84" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="54" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B85" s="57" t="n">
+        <v>4345</v>
+      </c>
+      <c r="C85" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="54" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B86" s="57" t="n">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="54" t="inlineStr">
+        <is>
+          <t>pbt</t>
+        </is>
+      </c>
+      <c r="B87" s="57" t="n">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="54" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B88" s="57" t="n">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="54" t="inlineStr">
+        <is>
+          <t>달러</t>
+        </is>
+      </c>
+      <c r="B89" s="57" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · 컨센서스 pre 2Q yahoo 2026-10-28</t>
+        </is>
+      </c>
+      <c r="B91" s="52" t="n"/>
+      <c r="C91" s="52" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B92" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C92" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="54" t="inlineStr">
+        <is>
+          <t>매출 avg</t>
+        </is>
+      </c>
+      <c r="B93" s="57" t="n">
+        <v>4270</v>
+      </c>
+      <c r="C93" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="54" t="inlineStr">
+        <is>
+          <t>매출 애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B94" s="57" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="54" t="inlineStr">
+        <is>
+          <t>EPS avg</t>
+        </is>
+      </c>
+      <c r="B95" s="55" t="n">
+        <v>214.9</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="54" t="inlineStr">
+        <is>
+          <t>EPS 애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B96" s="57" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · preview house estimate 2Q</t>
+        </is>
+      </c>
+      <c r="B98" s="52" t="n"/>
+      <c r="C98" s="52" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B99" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C99" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="54" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B100" s="57" t="n">
+        <v>4550</v>
+      </c>
+      <c r="C100" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="54" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="B101" s="57" t="n">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="54" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="B102" s="57" t="n">
+        <v>1780</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="54" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B103" s="55" t="n">
+        <v>245.9</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · 가이던스 revision</t>
+        </is>
+      </c>
+      <c r="B105" s="52" t="n"/>
+      <c r="C105" s="52" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B106" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C106" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="54" t="inlineStr">
+        <is>
+          <t>영업이익률 FY</t>
+        </is>
+      </c>
+      <c r="B107" s="55" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="C107" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="54" t="inlineStr">
+        <is>
+          <t>연구개발비</t>
+        </is>
+      </c>
+      <c r="B108" s="57" t="n">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="54" t="inlineStr">
+        <is>
+          <t>설비투자</t>
+        </is>
+      </c>
+      <c r="B109" s="57" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="54" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="B110" s="57" t="n">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · shareholder return</t>
+        </is>
+      </c>
+      <c r="B112" s="52" t="n"/>
+      <c r="C112" s="52" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B113" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C113" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="54" t="inlineStr">
+        <is>
+          <t>interim dps</t>
+        </is>
+      </c>
+      <c r="B114" s="57" t="n">
+        <v>49</v>
+      </c>
+      <c r="C114" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="54" t="inlineStr">
+        <is>
+          <t>직전 interim</t>
+        </is>
+      </c>
+      <c r="B115" s="57" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="54" t="inlineStr">
+        <is>
+          <t>직전 final</t>
+        </is>
+      </c>
+      <c r="B116" s="57" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="52" t="inlineStr">
+        <is>
+          <t>this quarter · shares</t>
+        </is>
+      </c>
+      <c r="B118" s="52" t="n"/>
+      <c r="C118" s="52" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B119" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C119" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="54" t="inlineStr">
+        <is>
+          <t>issued</t>
+        </is>
+      </c>
+      <c r="B120" s="57" t="n">
+        <v>732000000</v>
+      </c>
+      <c r="C120" s="56" t="inlineStr">
+        <is>
+          <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="54" t="inlineStr">
+        <is>
+          <t>treasury 0930</t>
+        </is>
+      </c>
+      <c r="B121" s="57" t="n">
+        <v>10047095</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="54" t="inlineStr">
+        <is>
+          <t>outstanding calc</t>
+        </is>
+      </c>
+      <c r="B122" s="57" t="n">
+        <v>721952905</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="52" t="inlineStr">
+        <is>
+          <t>consensus_yahoo_2026-10-28 · FY3/27</t>
+        </is>
+      </c>
+      <c r="B124" s="52" t="n"/>
+      <c r="C124" s="52" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B125" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C125" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="54" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B126" s="55" t="n">
+        <v>939.7</v>
+      </c>
+      <c r="C126" s="56" t="inlineStr">
+        <is>
+          <t>모두 발표 전 집계(10.28 기준) — 이번 실적 반영 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="54" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B127" s="57" t="n">
+        <v>17610</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="54" t="inlineStr">
+        <is>
+          <t>애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B128" s="57" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="52" t="inlineStr">
+        <is>
+          <t>consensus_yahoo_2026-10-28 · FY3/28</t>
+        </is>
+      </c>
+      <c r="B130" s="52" t="n"/>
+      <c r="C130" s="52" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B131" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C131" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="54" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B132" s="55" t="n">
+        <v>1218</v>
+      </c>
+      <c r="C132" s="56" t="inlineStr">
+        <is>
+          <t>모두 발표 전 집계(10.28 기준) — 이번 실적 반영 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="54" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B133" s="57" t="n">
+        <v>22621</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="54" t="inlineStr">
+        <is>
+          <t>애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B134" s="57" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="52" t="inlineStr">
+        <is>
+          <t>consensus_yahoo_2026-10-28 · 3Q_FY3/27</t>
+        </is>
+      </c>
+      <c r="B136" s="52" t="n"/>
+      <c r="C136" s="52" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B137" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C137" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="54" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B138" s="55" t="n">
+        <v>231.7</v>
+      </c>
+      <c r="C138" s="56" t="inlineStr">
+        <is>
+          <t>모두 발표 전 집계(10.28 기준) — 이번 실적 반영 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="54" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B139" s="57" t="n">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="52" t="inlineStr">
+        <is>
+          <t>컨센서스 yahoo 2026-10-28 · 목표주가 가격</t>
+        </is>
+      </c>
+      <c r="B141" s="52" t="n"/>
+      <c r="C141" s="52" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B142" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C142" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="54" t="inlineStr">
+        <is>
+          <t>평균</t>
+        </is>
+      </c>
+      <c r="B143" s="57" t="n">
+        <v>43495</v>
+      </c>
+      <c r="C143" s="56" t="inlineStr">
+        <is>
+          <t>모두 발표 전 집계(10.28 기준) — 이번 실적 반영 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="54" t="inlineStr">
+        <is>
+          <t>중앙값</t>
+        </is>
+      </c>
+      <c r="B144" s="57" t="n">
+        <v>43600</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="54" t="inlineStr">
+        <is>
+          <t>최고</t>
+        </is>
+      </c>
+      <c r="B145" s="57" t="n">
+        <v>55000</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="54" t="inlineStr">
+        <is>
+          <t>최저</t>
+        </is>
+      </c>
+      <c r="B146" s="57" t="n">
+        <v>23000</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="54" t="inlineStr">
+        <is>
+          <t>애널리스트 수</t>
+        </is>
+      </c>
+      <c r="B147" s="57" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="52" t="inlineStr">
+        <is>
+          <t>컨센서스 yahoo 2026-10-28 · surprises EPS %</t>
+        </is>
+      </c>
+      <c r="B149" s="52" t="n"/>
+      <c r="C149" s="52" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="53" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B150" s="53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C150" s="53" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="54" t="inlineStr">
+        <is>
+          <t>25.10</t>
+        </is>
+      </c>
+      <c r="B151" s="55" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C151" s="56" t="inlineStr">
+        <is>
+          <t>모두 발표 전 집계(10.28 기준) — 이번 실적 반영 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="54" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
+      </c>
+      <c r="B152" s="55" t="n">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="54" t="inlineStr">
+        <is>
+          <t>26.4</t>
+        </is>
+      </c>
+      <c r="B153" s="55" t="n">
+        <v>25.8</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="54" t="inlineStr">
+        <is>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="B154" s="55" t="n">
+        <v>42.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -20297,17 +21911,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="51" t="inlineStr">
+      <c r="B3" s="58" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="51" t="inlineStr">
+      <c r="C3" s="58" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
